--- a/output/pdf_financials_xlsx/KGS.xlsx
+++ b/output/pdf_financials_xlsx/KGS.xlsx
@@ -5424,19 +5424,19 @@
         <v>0.196429</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.522091</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.522091</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.318522</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.318522</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.399942</v>
       </c>
     </row>
     <row r="93">
@@ -8927,7 +8927,11 @@
           <t>Share-based payment reserve (note 6)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10108,7 +10112,11 @@
           <t>Share-based payment reserve (note 5)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -10476,7 +10484,11 @@
           <t>Share-based payment reserve (note 5)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KGS.xlsx
+++ b/output/pdf_financials_xlsx/KGS.xlsx
@@ -969,19 +969,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.02753</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008338999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004066</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005162</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000116</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1819,19 +1819,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.09243700000000001</v>
+        <v>-0.119967</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.097231</v>
+        <v>-0.10557</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.351385</v>
+        <v>-0.355451</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.125731</v>
+        <v>-0.130893</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.146502</v>
+        <v>-0.146386</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.190023</v>
@@ -1923,19 +1923,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.09243700000000001</v>
+        <v>-0.119967</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.097231</v>
+        <v>-0.10557</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.351385</v>
+        <v>-0.355451</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.125731</v>
+        <v>-0.130893</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.146502</v>
+        <v>-0.146386</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.190023</v>
@@ -2219,28 +2219,28 @@
         <v>0.004039</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.031983</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.32482</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.008233000000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.113243</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.012151</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.020696</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.059497</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.260914</v>
       </c>
     </row>
     <row r="35">
@@ -2323,28 +2323,28 @@
         <v>0.004039</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.031983</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.32482</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.008233000000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.113243</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.012151</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.020696</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.059497</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.260914</v>
       </c>
     </row>
     <row r="37">
@@ -2947,28 +2947,28 @@
         <v>0.221771</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.249695</v>
+        <v>0.217712</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.341872</v>
+        <v>0.017052</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.013235</v>
+        <v>0.005002</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.126881</v>
+        <v>0.013638</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.012183</v>
+        <v>3.2e-05</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.044913</v>
+        <v>0.024217</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.072769</v>
+        <v>0.013272</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.39438</v>
+        <v>0.133466</v>
       </c>
     </row>
     <row r="49">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11704,7 +11704,11 @@
           <t>RECLAMATION DEPOSIT</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -18577,7 +18581,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -21417,7 +21425,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -23737,7 +23749,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -24465,7 +24477,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -28364,7 +28376,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -30182,7 +30194,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -31545,7 +31557,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E266" s="5" t="n">

--- a/output/pdf_financials_xlsx/KGS.xlsx
+++ b/output/pdf_financials_xlsx/KGS.xlsx
@@ -5864,28 +5864,28 @@
         <v>0</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000941</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>-0.001</v>
+        <v>-0.004611</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.001</v>
+        <v>0.003483</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009018999999999999</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.011056</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.006874</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>0.009684999999999999</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003626</v>
       </c>
     </row>
     <row r="102">
@@ -6133,19 +6133,19 @@
         <v>-0.312372</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.105277</v>
+        <v>0.096258</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.370583</v>
+        <v>0.381639</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.37232</v>
+        <v>0.379194</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.021313</v>
+        <v>0.030998</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.017549</v>
+        <v>-0.021175</v>
       </c>
     </row>
     <row r="107">
@@ -6170,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>0.035639</v>
       </c>
       <c r="H107" s="3" t="n">
         <v>0</v>
@@ -6185,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.254487</v>
       </c>
       <c r="M107" s="3" t="n">
         <v>0</v>
@@ -13310,7 +13310,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -16069,7 +16073,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -18409,7 +18417,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -20780,7 +20792,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
